--- a/etf_holdings/2026-10-27_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.45%2385</t>
+          <t>+0.63%2400</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2400</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.50%7,700,000</t>
+          <t>14.63%7,700,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>14.63%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.36%1085</t>
+          <t>-2.3%1060</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.36%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.17%7,200,000</t>
+          <t>6.04%7,200,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.17%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.78%3145</t>
+          <t>-0.48%3130</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3145</v>
+        <v>3130</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.65%2,275,000</t>
+          <t>5.77%2,330,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2275000</v>
+        <v>2330000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.6%5070</t>
+          <t>-1.25%3960</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-1.25%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5070</v>
+        <v>3960</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.80%1,200,000</t>
+          <t>4.70%1,500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-7.12%6070</t>
+          <t>-3.46%5860</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6070</v>
+        <v>5860</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.79%1,000,000</t>
+          <t>4.64%1,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.79%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.14%4010</t>
+          <t>-6.31%4750</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.14%</t>
+          <t>-6.31%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4010</v>
+        <v>4750</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.75%1,500,000</t>
+          <t>4.51%1,200,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.51%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.19%7585</t>
+          <t>-2.04%7430</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.19%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7585</v>
+        <v>7430</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.07%680,000</t>
+          <t>4.00%680,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.3%4890</t>
+          <t>+2.76%521</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>+2.76%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4890</v>
+        <v>521</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.59%930,000</t>
+          <t>3.63%8,800,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>930000</v>
+        <v>8800000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4%1560</t>
+          <t>-2.04%4790</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1560</v>
+        <v>4790</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.57%2,900,000</t>
+          <t>3.53%930,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>2900000</v>
+        <v>930000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.46%507</t>
+          <t>-3.21%1510</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.46%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>507</v>
+        <v>1510</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.52%8,800,000</t>
+          <t>3.47%2,900,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.47%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>8800000</v>
+        <v>2900000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.38%986</t>
+          <t>-4.56%941</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-4.56%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>986</v>
+        <v>941</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.46%4,450,000</t>
+          <t>3.32%4,450,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.6%1265</t>
+          <t>-0.79%1255</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1265</v>
+        <v>1255</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.01%3,010,000</t>
+          <t>2.99%3,010,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.99%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.08%301</t>
+          <t>+5.98%1950</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.08%</t>
+          <t>+5.98%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>301</v>
+        <v>1950</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.85%12,000,000</t>
+          <t>2.86%1,850,956</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.86%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>12000000</v>
+        <v>1850956</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.33%1420</t>
+          <t>-1.16%297.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1420</v>
+        <v>297.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.69%2,400,000</t>
+          <t>2.83%12,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2400000</v>
+        <v>12000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:33</t>
+          <t>2026-10-27 22:42:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.13%1840</t>
+          <t>-9.86%1280</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.13%</t>
+          <t>-9.86%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1840</v>
+        <v>1280</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.69%1,850,956</t>
+          <t>2.43%2,400,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1850956</v>
+        <v>2400000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.02%1560</t>
+          <t>-0.85%1760</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>-0.85%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1560</v>
+        <v>1760</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.32%1,880,000</t>
+          <t>2.23%1,600,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>1880000</v>
+        <v>1600000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.2%1775</t>
+          <t>-6.09%1465</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1775</v>
+        <v>1465</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.24%1,600,000</t>
+          <t>2.18%1,880,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1600000</v>
+        <v>1880000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,25 +1541,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.85%1875</t>
+          <t>+0.03%16015</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1875</v>
+        <v>16015</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.16%1,460,000</t>
+          <t>2.16%170,500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1460000</v>
+        <v>170500</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.06%16010</t>
+          <t>-7.47%1735</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.06%</t>
+          <t>-7.47%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>16010</v>
+        <v>1735</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.98%156,500</t>
+          <t>2.01%1,460,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>156500</v>
+        <v>1460000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.08%6175</t>
+          <t>-2.83%6000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-2.83%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6175</v>
+        <v>6000</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.83%375,000</t>
+          <t>1.78%375,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.95%125.5</t>
+          <t>+6.52%441</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+6.52%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>125.5</v>
+        <v>441</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.99%10,000,000</t>
+          <t>0.98%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>10000000</v>
+        <v>2800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-5.15%414</t>
+          <t>+2.48%269</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.15%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>414</v>
+        <v>269</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.92%2,800,000</t>
+          <t>0.85%4,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2800000</v>
+        <v>4000000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.58%262.5</t>
+          <t>-3.14%1080</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.58%</t>
+          <t>-3.14%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>262.5</v>
+        <v>1080</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.83%4,000,000</t>
+          <t>0.70%820,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>4000000</v>
+        <v>820000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.69%1115</t>
+          <t>+0.56%9810</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1115</v>
+        <v>9810</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.72%820,000</t>
+          <t>0.70%90,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>820000</v>
+        <v>90000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.22%9755</t>
+          <t>+1.02%247.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>+1.02%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9755</v>
+        <v>247.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.69%90,000</t>
+          <t>0.63%3,200,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>90000</v>
+        <v>3200000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,34 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2%245</t>
+          <t>-2.39%122.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-2.39%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>245</v>
+        <v>122.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.62%3,200,000</t>
+          <t>0.58%6,000,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.58%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3200000</v>
+        <v>6000000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.51%2335</t>
+          <t>-3.64%2250</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.51%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2335</v>
+        <v>2250</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.57%310,000</t>
+          <t>0.55%310,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-5.33%320</t>
+          <t>+2.19%327</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>+2.19%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.51%2,000,000</t>
+          <t>0.52%2,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.78%424</t>
+          <t>+1.18%429</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.78%</t>
+          <t>+1.18%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.50%1,500,000</t>
+          <t>0.51%1,500,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:35</t>
+          <t>2026-10-27 22:42:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6%1410</t>
+          <t>-2.13%1380</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-6%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1410</v>
+        <v>1380</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.39%350,000</t>
+          <t>0.38%350,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.19%594</t>
+          <t>-0.34%592</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.38%800,000</t>
+          <t>0.37%800,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.44%113.5</t>
+          <t>+0.44%114</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>113.5</v>
+        <v>114</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.65%224.5</t>
+          <t>-3.79%216</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.65%</t>
+          <t>-3.79%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>224.5</v>
+        <v>216</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.35%2,000,000</t>
+          <t>0.34%2,000,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-3.53%846</t>
+          <t>-1.65%832</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-3.53%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.14%826</t>
+          <t>-0.46%651</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.14%</t>
+          <t>-0.46%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>826</v>
+        <v>651</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.20%300,000</t>
+          <t>0.21%400,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.79%467</t>
+          <t>-1.45%814</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.79%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>467</v>
+        <v>814</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.07%200,000</t>
+          <t>0.19%300,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>200000</v>
+        <v>300000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2883凱基金</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.69%230</t>
+          <t>+1.85%38.45</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-6.69%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>230</v>
+        <v>38.45</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.06%350,000</t>
+          <t>0.12%4,000,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>350000</v>
+        <v>4000000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2883凱基金</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.31%37.75</t>
+          <t>-0.21%466</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.31%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>37.75</v>
+        <v>466</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.06%2,000,000</t>
+          <t>0.07%200,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.04%255.5</t>
+          <t>-0.87%228</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.04%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>255.5</v>
+        <v>228</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.06%300,000</t>
+          <t>0.06%350,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>300000</v>
+        <v>350000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-3.79%68.5</t>
+          <t>-1.17%252.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-1.17%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>68.5</v>
+        <v>252.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.05%900,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>900000</v>
+        <v>300000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-3.46%153.5</t>
+          <t>+0.15%68.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>153.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.04%350,000</t>
+          <t>0.05%900,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>350000</v>
+        <v>900000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-6.98%246.5</t>
+          <t>-2.28%150</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>246.5</v>
+        <v>150</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.04%350,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1000</v>
+        <v>350000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-9.02%438.5</t>
+          <t>+0.61%248</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.02%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>438.5</v>
+        <v>248</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.59%1880</t>
+          <t>-4.1%420.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1880</v>
+        <v>420.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:36</t>
+          <t>2026-10-27 22:42:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,21 +3188,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.93%597</t>
+          <t>+1.6%1910</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>597</v>
+        <v>1910</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:37</t>
+          <t>2026-10-27 22:42:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-6.77%248</t>
+          <t>-2.18%584</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-6.77%</t>
+          <t>-2.18%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>248</v>
+        <v>584</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:37</t>
+          <t>2026-10-27 22:42:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.92%299</t>
+          <t>+2.62%254.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>299</v>
+        <v>254.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:37</t>
+          <t>2026-10-27 22:42:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.49%1980</t>
+          <t>+9.87%328.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>+9.87%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1980</v>
+        <v>328.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:37</t>
+          <t>2026-10-27 22:42:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-3.13%154.5</t>
+          <t>-1.26%1955</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-3.13%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>154.5</v>
+        <v>1955</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-27 00:07:37</t>
+          <t>2026-10-27 22:42:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-4.39%654</t>
+          <t>+5.5%163</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+5.5%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>654</v>
+        <v>163</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-27_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-27_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-27 22:54:46</t>
+          <t>2026-10-27 23:22:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1393,6 +1393,2141 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-0.85%1760</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-0.85%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1760</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.23%1,600,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-6.09%1465</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.09%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1465</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2.18%1,880,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2.18%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.14%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5274信驊</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>+0.03%16015</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>+0.03%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>16015</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2.16%170,500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2.16%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>170500</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-7.47%1735</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-7.47%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1735</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.01%1,460,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1460000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.16%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-2.83%6000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-2.83%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.78%375,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.78%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>375000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2408南亞科</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+6.52%441</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>+6.52%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>441</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.98%2,800,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.98%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>+0.06%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2449京元電子</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+2.48%269</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>+2.48%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>269</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.85%4,000,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.85%</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2368金像電</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-3.14%1080</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-3.14%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1080</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.70%820,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>820000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2059川湖</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>+0.56%9810</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>+0.56%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>9810</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.70%90,000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.70%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>90000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2317鴻海</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>+1.02%247.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>+1.02%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>247.5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.63%3,200,000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2303聯電</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-2.39%122.5</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-2.39%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.58%6,000,000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.58%</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>6805富世達</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-3.64%2250</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-3.64%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2250</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.55%310,000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>310000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3211順達</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+2.19%327</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>+2.19%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>327</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.52%2,000,000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3450聯鈞</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>+1.18%429</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>+1.18%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>429</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.51%1,500,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.51%</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:13</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>6442光聖</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-2.13%1380</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1380</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.38%350,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3583辛耘</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-0.34%592</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-0.34%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>592</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.37%800,000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>800000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2882國泰金</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+0.44%114</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>114</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.36%4,000,000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-3.79%216</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-3.79%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>216</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.34%2,000,000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1560中砂</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-1.65%832</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-1.65%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>832</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.32%480,000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>480000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-0.46%651</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>651</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.21%400,000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>6488環球晶</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-1.45%814</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>814</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.19%300,000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2883凱基金</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>+1.85%38.45</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>+1.85%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>38.45</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.12%4,000,000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.12%</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-0.21%466</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-0.21%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>466</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.07%200,000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>6285啟碁</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-0.87%228</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-0.87%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>228</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.06%350,000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2301光寶科</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-1.17%252.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-1.17%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>252.5</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.06%300,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.06%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>300000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1717長興</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>+0.15%68.6</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.05%900,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>900000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2481強茂</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-2.28%150</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-2.28%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>150</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.04%350,000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>350000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3264欣銓</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>+0.61%248</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>+0.61%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>248</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>8358金居</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-4.1%420.5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-4.1%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>420.5</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:14</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8299群聯</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>+1.6%1910</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>+1.6%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1910</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:16</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6196帆宣</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-2.18%584</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-2.18%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>584</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:16</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>6239力成</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+2.62%254.5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>+2.62%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>254.5</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:16</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2049上銀</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+9.87%328.5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+9.87%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>328.5</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:16</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-1.26%1955</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-1.26%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>1955</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-27 23:22:16</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2344華邦電</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+5.5%163</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>163</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
